--- a/artfynd/A 19520-2023 artfynd.xlsx
+++ b/artfynd/A 19520-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19520-2023 artfynd.xlsx
+++ b/artfynd/A 19520-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96005193</v>
+        <v>111059869</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>2682</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öd, Östersund, Jmt</t>
+          <t>Öd, Fugelstabodarna, Marieby, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483996.7822590692</v>
+        <v>483952</v>
       </c>
       <c r="R2" t="n">
-        <v>6998799.397782398</v>
+        <v>6998850</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,33 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96005419</v>
+        <v>96005193</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,36 +788,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Öd, Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484055.7852062305</v>
+        <v>483996</v>
       </c>
       <c r="R3" t="n">
-        <v>6998725.338477203</v>
+        <v>6998800</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,19 +846,9 @@
           <t>2021-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,52 +875,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96005175</v>
+        <v>110098857</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öd, Östersund, Jmt</t>
+          <t>Gubbslutet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483996.7822590692</v>
+        <v>484003</v>
       </c>
       <c r="R4" t="n">
-        <v>6998799.397782398</v>
+        <v>6998760</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,22 +941,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,32 +983,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96005236</v>
+        <v>110099051</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>221137</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,17 +1013,16 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Gubbslutet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484031.4180273722</v>
+        <v>483964</v>
       </c>
       <c r="R5" t="n">
-        <v>6998746.729290233</v>
+        <v>6998857</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,22 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96005275</v>
+        <v>96005162</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,14 +1124,14 @@
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Öd, Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484028.2903625954</v>
+        <v>483996</v>
       </c>
       <c r="R6" t="n">
-        <v>6998755.796080087</v>
+        <v>6998800</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,19 +1161,9 @@
           <t>2021-09-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96005323</v>
+        <v>96005236</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484054.5035895148</v>
+        <v>484031</v>
       </c>
       <c r="R7" t="n">
-        <v>6998741.184778185</v>
+        <v>6998747</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,19 +1260,9 @@
           <t>2021-09-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,15 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96005330</v>
+        <v>96005243</v>
       </c>
       <c r="B8" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484053.5883161842</v>
+        <v>484028</v>
       </c>
       <c r="R8" t="n">
-        <v>6998739.379000639</v>
+        <v>6998756</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1433,19 +1359,9 @@
           <t>2021-09-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,15 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110098706</v>
+        <v>96005323</v>
       </c>
       <c r="B9" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,16 +1418,17 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gubbslutet, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484031.0495887363</v>
+        <v>484055</v>
       </c>
       <c r="R9" t="n">
-        <v>6998763.928699366</v>
+        <v>6998742</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,22 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,51 +1487,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110098857</v>
+        <v>96005330</v>
       </c>
       <c r="B10" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gubbslutet, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484003.3832926349</v>
+        <v>484054</v>
       </c>
       <c r="R10" t="n">
-        <v>6998759.539476228</v>
+        <v>6998739</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,22 +1554,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,15 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110098677</v>
+        <v>96005419</v>
       </c>
       <c r="B11" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,16 +1616,17 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gubbslutet, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484046.4042256264</v>
+        <v>484055</v>
       </c>
       <c r="R11" t="n">
-        <v>6998752.991444721</v>
+        <v>6998725</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1769,22 +1653,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,12 +1688,7 @@
         <v>110097575</v>
       </c>
       <c r="B12" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483952.7615686469</v>
+        <v>483953</v>
       </c>
       <c r="R12" t="n">
-        <v>6998786.943706508</v>
+        <v>6998786</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,15 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110098001</v>
+        <v>110097930</v>
       </c>
       <c r="B13" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484090.6582356532</v>
+        <v>484060</v>
       </c>
       <c r="R13" t="n">
-        <v>6998720.64136113</v>
+        <v>6998700</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,15 +1901,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110098894</v>
+        <v>110098001</v>
       </c>
       <c r="B14" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484008.3638088156</v>
+        <v>484091</v>
       </c>
       <c r="R14" t="n">
-        <v>6998758.60975928</v>
+        <v>6998720</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +1972,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +1982,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,15 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110097930</v>
+        <v>110098544</v>
       </c>
       <c r="B15" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484060.1946265645</v>
+        <v>484085</v>
       </c>
       <c r="R15" t="n">
-        <v>6998700.425209036</v>
+        <v>6998729</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2080,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2090,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,15 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110098544</v>
+        <v>110098677</v>
       </c>
       <c r="B16" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484085.713197374</v>
+        <v>484046</v>
       </c>
       <c r="R16" t="n">
-        <v>6998728.811945172</v>
+        <v>6998753</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2376,15 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110098916</v>
+        <v>110098706</v>
       </c>
       <c r="B17" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483993.9603890106</v>
+        <v>484032</v>
       </c>
       <c r="R17" t="n">
-        <v>6998778.593792586</v>
+        <v>6998763</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2452,7 +2296,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2306,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,6 +2330,222 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110098894</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gubbslutet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>484008</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6998759</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>110098916</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gubbslutet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>483994</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6998778</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19520-2023 artfynd.xlsx
+++ b/artfynd/A 19520-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111059869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005193</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110098857</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110099051</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005162</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005236</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005243</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005323</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005330</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005419</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110097575</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +1958,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110097930</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2006,6 +2071,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110098001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110098544</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2222,6 +2297,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110098677</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2330,6 +2410,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110098706</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2438,6 +2523,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110098894</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2546,8 +2636,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110098916</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>